--- a/KEIKI_RegularSofa_新标题.xlsx
+++ b/KEIKI_RegularSofa_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Chaise Turtle Velvet Corduroy Loveseat Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge White</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant White</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Chaise Turtle Velvet Corduroy Loveseat Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Dark Gray</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Dark Gray</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Chaise Turtle Velvet Corduroy Loveseat Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch with Rotating Side Table Memory Foam for Living Room Comfy Lounge Pink</t>
+          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Pink</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch with Rotating Side Table Memory Foam for Living Room Comfy Lounge Black</t>
+          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Chaise Sofa Couch Memory Foam for Living Room Flexible Layout Comfy Lounge Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Coffee</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch with Rotating Side Table Memory Foam for Living Room Comfy Lounge Gray</t>
+          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Gray</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch with Rotating Side Table Memory Foam for Living Room Comfy Lounge Beige</t>
+          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 172" 6Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Beige</t>
+          <t>KEIKI 172" 6Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 149" 5Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Beige</t>
+          <t>KEIKI 149" 5Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Loveseat Sofa Couch for Living Room Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 63" 2Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Loveseat Sofa Couch for Living Room Deep Seat Comfy Lounge Beige</t>
+          <t>KEIKI 63" 2Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Beige</t>
+          <t>KEIKI 86" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 86" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Chaise Sofa Couch Memory Foam for Living Room Flexible Layout Comfy Lounge Gray</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Gray</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Chaise Sofa Couch Memory Foam for Living Room Flexible Layout Comfy Lounge Black</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Chaise Sofa Couch Memory Foam for Living Room Flexible Layout Comfy Lounge Pink</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Pink</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Chaise Sofa Couch Memory Foam for Living Room Flexible Layout Comfy Lounge Beige</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Black</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Dark Gray</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Dark Gray</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Dark Gray</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Dark Gray</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge White</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge White</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge White</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge White</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Light Gray</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Light Gray</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Light Gray</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Deep Seat Comfy Lounge Light Gray</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Grey</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Grey</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Chaise Loveseat Sofa Couch for Living Room Flexible Layout Comfy Lounge Grey</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Grey</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Chaise Loveseat Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Yellow</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Chaise Loveseat Sofa Couch for Living Room Flexible Layout Comfy Lounge Yellow</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Gray</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Gray</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Chaise Sofa Couch for Living Room Flexible Layout Comfy Lounge Yellow</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Green</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Gray</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Gray</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Blue</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Black</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Dark Green</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Green</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Pink</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Pink</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Coffee</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Flexible Layout Comfy Lounge Beige</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
         </is>
       </c>
     </row>

--- a/KEIKI_RegularSofa_新标题.xlsx
+++ b/KEIKI_RegularSofa_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant White</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Dark Gray</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Sofa Couch with Chaise for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Pink</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Black</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Gray</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Sectional Velvet Sofa Couch with Rotating Side Table for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Beige</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Gray</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Pink</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Gray</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive White</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Deep Seat Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Gray</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Grey</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Grey</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Grey</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Grey</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Gray</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Gray</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious G...</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch for Living Room Home Bedroom Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Inviting Warm Spacious Y...</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Gray</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Blue</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Black</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Dark Green</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Pink</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch for Living Room Apartment Small Space Flexible Layout Cozy Soft Plush Comfy Relaxing Lounge Modern Elegant Stylish Comfortable Supportive Beige</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
         </is>
       </c>
     </row>

--- a/KEIKI_RegularSofa_新标题.xlsx
+++ b/KEIKI_RegularSofa_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Modern Home Apartment Living Flexible Layout Deep Seat Clean Bright Perfect for Relaxing Lounge Space M...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Executive Suite Small Space Adjustable Configuration Plush Cushions Professional Refined Ideal for Ente...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Rel...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Sp...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Feminine Retreat Home Office Customizable Setup Romantic Dreamy Designed for Comfort Lounge Space Glam Design Pink</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Urban Loft Apartment Living Flexible Layout Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Contemporary Home Small Space Adjustable Configuration Plush Cushions Comfortable Inviting Ideal for Entertaining Loun...</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design Gray</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Living Room Bedroom Apartment Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Des...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Cozy Cottage Home Office Customizable Setup Warm Inviting Designed for Comfort Lounge Space Traditional Design Beige</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Plush Cushions Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfor...</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design High Quality Comfortable S...</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resil...</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Cozy Cottage Home Office Customizable Setup Comfy Support Warm Inviting Designed for Comfort Lounge Space Traditional Design High Quality Comfortable Sup...</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortable Supportive...</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Plush Cushions Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfort...</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Cozy Cottage Bedroom Studio Versatile Arrangement Spacious Design Warm Inviting Great for Lounging Lounge Space Traditional Design High Quality Comfortabl...</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Living Room Home Office Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design High Density Foam Cushions Resili...</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Comfy Support Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supporti...</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for City Apartment Apartment Living Flexible Layout Deep Seat Neutral Calm Perfect for Relaxing Lounge Space Modern Design...</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Urban Loft Small Space Adjustable Configuration Plush Cushions Sleek Bold Ideal for Entertaining Lounge Space Contempo...</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Feminine Retreat Bedroom Studio Versatile Arrangement Spacious Design Romantic Dreamy Great for Lounging Lounge Space ...</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Asse...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Cozy Cottage Home Office Customizable Setup Comfy Support Warm Inviting Designed for Comfort Lounge Space Traditional ...</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortabl...</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Urban Loft Small Space Adjustable Configuration Plush Cushions Sleek Bold Ideal for Entertaining Lounge Space Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Black</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Urban Loft Home Office Customizable Setup Comfy Support Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comforta...</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Executive Suite Apartment Living Flexible Layout Deep Seat Professional Refined Perfect for Relaxing Lounge Space Luxury Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Executive Suite Small Space Adjustable Configuration Plush Cushions Professional Refined Ideal for Entertaining Lounge Space Luxury Design Dar...</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Executive Suite Bedroom Studio Versatile Arrangement Spacious Design Professional Refined Great for Lounging Lounge Space Luxury Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Dark ...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Executive Suite Home Office Customizable Setup Comfy Support Professional Refined Designed for Comfort Lounge Space Luxury Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Modern Home Apartment Living Flexible Layout Deep Seat Clean Bright Perfect for Relaxing Lounge Space Minimalist Design High Quality Comfortab...</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Modern Home Small Space Adjustable Configuration Plush Cushions Clean Bright Ideal for Entertaining Lounge Space Minimalist Design White</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Modern Home Bedroom Studio Versatile Arrangement Spacious Design Clean Bright Great for Lounging Lounge Space Minimalist Design White</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design White</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Modern Home Home Office Customizable Setup Comfy Support Clean Bright Designed for Comfort Lounge Space Minimalist Design High Quality Comfort...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Contemporary Home Apartment Living Flexible Layout Deep Seat Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Contemporary Home Small Space Adjustable Configuration Plush Cushions Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design L...</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Spacious Design Comfortable Inviting Great for Lounging Lounge Space Modern Design Ligh...</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Living Room Home Office Flexible Layout Deep Seat Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Contemporary Home Home Office Customizable Setup Comfy Support Comfortable Inviting Designed for Comfort Lounge Space Modern Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Grey</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for City Apartment Apartment Living Flexible Layout Neutral Calm Perfect for Relaxing Lounge Space Modern Design High Quality Comfortab...</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Grey</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design Grey</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comforta...</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable ...</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Apartment Living Flexible Layout Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Small Space Adjustable Configuration Happy Optimistic Ideal for Entertaining Lounge Space Mid Century Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Gray</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design High Quality Comfort...</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable ...</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Living Room Home Office Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Yellow</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Apartment Living Flexible Layout Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppor...</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant ...</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive El...</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Series High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant ...</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive El...</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant G...</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Green</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive Ele...</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive El...</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Series High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive El...</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegan...</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive Ele...</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegant...</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Blue</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Elega...</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable S...</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Series High Quality Comfortable Support...</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable S...</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Series High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Series High Quality Comfort Style 6 Sup...</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppor...</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Light Coffee</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportive...</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Support...</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable S...</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Series High Quality Comfortab Style 3 Sup...</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Support...</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable S...</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppo...</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportiv...</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Lounge Seating Perfect for Relaxing Easy Assembly Modern Design Beige White</t>
+          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Supporti...</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design High Quality Comfor...</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfort...</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Su...</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Dark Green</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Feminine Retreat Small Space Adjustable Configuration Romantic Dreamy Ideal for Entertaining Lounge Space Glam Design Pink</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design Coffee</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Living Room Apartment Small Space Flexible Layout Soft Plush Comfortable Comfy Lounge Seating Perfect for Relaxing Easy Assembly Moder...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Cozy Cottage Home Office Customizable Setup Warm Inviting Designed for Comfort Lounge Space Traditional Design High Quality Comfortabl...</t>
         </is>
       </c>
     </row>

--- a/KEIKI_RegularSofa_新标题.xlsx
+++ b/KEIKI_RegularSofa_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Modern Home Apartment Living Flexible Layout Deep Seat Clean Bright Perfect for Relaxing Lounge Space M...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Bright Modern Home Compact Studio Comfort Seekers Minimalists Adaptable Relaxation Seekers Ultra Soft Plush ...</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Executive Suite Small Space Adjustable Configuration Plush Cushions Professional Refined Ideal for Ente...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Executive Suite Compact Studio Comfort Seekers Luxury Buyers Adaptable Relaxation Seekers Ultra Soft Plush I...</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Sectional Corduroy Loveseat Sofa Couch with Chaise for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Sp...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Adaptable Relaxation Seekers Ultra Soft P...</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Feminine Retreat Home Office Customizable Setup Romantic Dreamy Designed for Comfort Lounge Space Glam Design Pink</t>
+          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Feminine Retreat Compact Studio Style Conscious Glam Seekers Practical Buyers Luxuriously Soft Designed f...</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Urban Loft Apartment Living Flexible Layout Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design Black</t>
+          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perf...</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Contemporary Home Small Space Adjustable Configuration Plush Cushions Comfortable Inviting Ideal for Entertaining Loun...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft L...</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design Gray</t>
+          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Great for Intimat...</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Cozy Cottage Home Office Customizable Setup Warm Inviting Designed for Comfort Lounge Space Traditional Design Beige</t>
+          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Design...</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 172" 6Seat Modular Velvet Sofa Couch for Industrial Loft Great Room Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perfect for Bold Sophisticated Relaxation Glam M...</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Plush Cushions Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfor...</t>
+          <t>KEIKI 172" 6Seat Modular Velvet Sofa Couch for Cozy Cottage Great Room Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Beige</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design High Quality Comfortable S...</t>
+          <t>KEIKI 149" 5Seat Modular Velvet Sofa Couch for Industrial Loft Open Concept Living Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Great for Spacious Gathering Area Glam ...</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Cozy Cottage Home Office Customizable Setup Comfy Support Warm Inviting Designed for Comfort Lounge Space Traditional Design High Quality Comfortable Sup...</t>
+          <t>KEIKI 149" 5Seat Modular Velvet Sofa Couch for Cozy Cottage Open Concept Living Style Conscious Traditional Families Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortable Supportive...</t>
+          <t>KEIKI 63" 2Seat Modular Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perfect for Bold Sophisticated Relax...</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Adjustable Configuration Plush Cushions Warm Inviting Ideal for Entertaining Lounge Space Traditional Design High Quality Comfort...</t>
+          <t>KEIKI 63" 2Seat Modular Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Gl...</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Cozy Cottage Bedroom Studio Versatile Arrangement Spacious Design Warm Inviting Great for Lounging Lounge Space Traditional Design High Quality Comfortabl...</t>
+          <t>KEIKI 86" 3Seat Modular Velvet Sofa Couch for Cozy Cottage Small Apartment Style Conscious Traditional Families Practical Buyers Luxuriously Soft Great for Functional Relaxation Spot Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Urban Loft Home Office Customizable Setup Comfy Support Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Supporti...</t>
+          <t>KEIKI 86" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam Modern Black</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for City Apartment Apartment Living Flexible Layout Deep Seat Neutral Calm Perfect for Relaxing Lounge Space Modern Design...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Rela...</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Urban Loft Small Space Adjustable Configuration Plush Cushions Sleek Bold Ideal for Entertaining Lounge Space Contempo...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Ideal for Luxur...</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Feminine Retreat Bedroom Studio Versatile Arrangement Spacious Design Romantic Dreamy Great for Lounging Lounge Space ...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Feminine Retreat Small Apartment Style Conscious Glam Seekers Adaptable Homeowners Luxuriously Soft Great for Functional ...</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch with Chaise Memory Foam for Cozy Cottage Home Office Customizable Setup Comfy Support Warm Inviting Designed for Comfort Lounge Space Traditional ...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Cozy Cottage Small Apartment Style Conscious Traditional Families Adaptable Homeowners Luxuriously Soft Designed for Flex...</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Urban Loft Apartment Living Flexible Layout Deep Seat Sleek Bold Perfect for Relaxing Lounge Space Contemporary Design High Quality Comfortabl...</t>
+          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Industrial Loft Great Room Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Perfect for Bold Sophisticated Relaxation Gl...</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Urban Loft Small Space Adjustable Configuration Plush Cushions Sleek Bold Ideal for Entertaining Lounge Space Contemporary Design Black</t>
+          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Industrial Loft Open Concept Living Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging...</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Urban Loft Bedroom Studio Versatile Arrangement Spacious Design Sleek Bold Great for Lounging Lounge Space Contemporary Design Black</t>
+          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Industrial Loft Family Living Room Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Spac...</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Urban Loft Home Office Customizable Setup Comfy Support Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comforta...</t>
+          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Gla...</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Executive Suite Apartment Living Flexible Layout Deep Seat Professional Refined Perfect for Relaxing Lounge Space Luxury Design Dark Gray</t>
+          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Executive Suite Great Room Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Perfect for Professional Refined Relaxation Glam M...</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Executive Suite Small Space Adjustable Configuration Plush Cushions Professional Refined Ideal for Entertaining Lounge Space Luxury Design Dar...</t>
+          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Executive Suite Open Concept Living Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam ...</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Executive Suite Bedroom Studio Versatile Arrangement Spacious Design Professional Refined Great for Lounging Lounge Space Luxury Design Dark Gray</t>
+          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Executive Suite Family Living Room Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam...</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Executive Suite Home Office Customizable Setup Comfy Support Professional Refined Designed for Comfort Lounge Space Luxury Design Dark Gray</t>
+          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Executive Suite Small Apartment Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Modern Home Apartment Living Flexible Layout Deep Seat Clean Bright Perfect for Relaxing Lounge Space Minimalist Design High Quality Comfortab...</t>
+          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Bright Modern Home Great Room Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Perfect for Clean Airy Feel Relaxation Glam Moder...</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Modern Home Small Space Adjustable Configuration Plush Cushions Clean Bright Ideal for Entertaining Lounge Space Minimalist Design White</t>
+          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Bright Modern Home Open Concept Living Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam...</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Modern Home Bedroom Studio Versatile Arrangement Spacious Design Clean Bright Great for Lounging Lounge Space Minimalist Design White</t>
+          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Bright Modern Home Family Living Room Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Gla...</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Modern Home Home Office Customizable Setup Comfy Support Clean Bright Designed for Comfort Lounge Space Minimalist Design High Quality Comfort...</t>
+          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Bright Modern Home Small Apartment Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mod...</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Sectional Sofa Couch for Contemporary Home Apartment Living Flexible Layout Deep Seat Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Light Gray</t>
+          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Modern Home Great Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light Gray</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Sectional Sofa Couch for Contemporary Home Small Space Adjustable Configuration Plush Cushions Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design L...</t>
+          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Modern Home Open Concept Living Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern ...</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Sectional Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Spacious Design Comfortable Inviting Great for Lounging Lounge Space Modern Design Ligh...</t>
+          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Sectional Sofa Couch for Contemporary Home Home Office Customizable Setup Comfy Support Comfortable Inviting Designed for Comfort Lounge Space Modern Design Light Gray</t>
+          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Ligh...</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for City Apartment Apartment Living Flexible Layout Neutral Calm Perfect for Relaxing Lounge Space Modern Design High Quality Comfortab...</t>
+          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for City Apartment Small Apartment Style Conscious Practical Buyers Adaptable Homeowners Luxuriously Soft Perfect for Balanced Neutral Rel...</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design Grey</t>
+          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for City Apartment Compact Studio Style Conscious Practical Buyers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously So...</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comforta...</t>
+          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot ...</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable ...</t>
+          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configu...</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Apartment Living Flexible Layout Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
+          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam M...</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Small Space Adjustable Configuration Happy Optimistic Ideal for Entertaining Lounge Space Mid Century Design Yellow</t>
+          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Loungi...</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for City Apartment Bedroom Studio Versatile Arrangement Neutral Calm Great for Lounging Lounge Space Modern Design High Quality Comfort...</t>
+          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space ...</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable ...</t>
+          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuratio...</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Sectional Sofa Couch with Chaise for Sunny Apartment Apartment Living Flexible Layout Happy Optimistic Perfect for Relaxing Lounge Space Mid Century Design Yellow</t>
+          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Gla...</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable Su...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppor...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Be...</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant ...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam Mod...</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive El...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Series High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern ...</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant ...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive El...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern ...</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Garden Home Bedroom Studio Versatile Arrangement Fresh Natural Great for Lounging Lounge Space Organic Design High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Home Office Customizable Setup Fresh Natural Designed for Comfort Lounge Space Organic Design High Quality Comfortable Supportive Elegant Green</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam ...</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Apartment Living Flexible Layout Fresh Natural Perfect for Relaxing Lounge Space Organic Design High Quality Comfortable Supportive Elegant G...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam...</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Garden Home Small Space Adjustable Configuration Fresh Natural Ideal for Entertaining Lounge Space Organic Design High Quality Comfortable Supportive Ele...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam ...</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive El...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Mod...</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Moder...</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Glam Mo...</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Series High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Blue</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive El...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern ...</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegan...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Blue</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Eleg...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Glam Moder...</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Coastal Home Small Space Adjustable Configuration Serene Peaceful Ideal for Entertaining Lounge Space Hamptons Design High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Blue</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfortable Supportive Ele...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Home Office Customizable Setup Serene Peaceful Designed for Comfort Lounge Space Hamptons Design High Quality Comfortable Supportive Elegant...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam M...</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Coastal Home Apartment Living Flexible Layout Serene Peaceful Perfect for Relaxing Lounge Space Hamptons Design High Quality Comfortable Supportive Elega...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Gla...</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable S...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern L...</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppo...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern L...</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Series High Quality Comfortable Support...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light...</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Series High Quality Comfortable S...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Ligh...</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Series High Quality Comfortable Suppo...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Lig...</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Series High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Ligh...</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Series High Quality Comfort Style 6 Sup...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light...</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable Su...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppor...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Li...</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportive...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Support...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Be...</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable S...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern B...</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppo...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Series High Quality Comfortab Style 3 Sup...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Beig...</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Support...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Beige...</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Small Space Adjustable Configuration Comfortable Inviting Ideal for Entertaining Lounge Space Modern Design High Quality Comfortable S...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Beig...</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design High Quality Comfortable Suppo...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Bei...</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Sofa Couch for Contemporary Home Home Office Customizable Setup Comfortable Inviting Designed for Comfort Lounge Space Modern Design High Quality Comfortable Supportiv...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Beig...</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Sofa Couch for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design High Quality Comfortable Supporti...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Moder...</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for City Apartment Small Space Adjustable Configuration Neutral Calm Ideal for Entertaining Lounge Space Modern Design High Quality Comfor...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Gray</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Coastal Home Bedroom Studio Versatile Arrangement Serene Peaceful Great for Lounging Lounge Space Hamptons Design High Quality Comfort...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern ...</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Urban Loft Home Office Customizable Setup Sleek Bold Designed for Comfort Lounge Space Contemporary Design High Quality Comfortable Su...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Gla...</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Contemporary Home Apartment Living Flexible Layout Comfortable Inviting Perfect for Relaxing Lounge Space Modern Design Dark Green</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Dark ...</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Feminine Retreat Small Space Adjustable Configuration Romantic Dreamy Ideal for Entertaining Lounge Space Glam Design Pink</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Feminine Retreat Small Apartment Style Conscious Glam Seekers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Contemporary Home Bedroom Studio Versatile Arrangement Comfortable Inviting Great for Lounging Lounge Space Modern Design Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Coffee</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Sectional Sofa Couch Storage for Cozy Cottage Home Office Customizable Setup Warm Inviting Designed for Comfort Lounge Space Traditional Design High Quality Comfortabl...</t>
+          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Cozy Cottage Small Apartment Style Conscious Traditional Families Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam ...</t>
         </is>
       </c>
     </row>

--- a/KEIKI_RegularSofa_新标题.xlsx
+++ b/KEIKI_RegularSofa_新标题.xlsx
@@ -494,7 +494,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Bright Modern Home Compact Studio Comfort Seekers Minimalists Adaptable Relaxation Seekers Ultra Soft Plush ...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Turtle Velvet Loveseat Sofa Couch with Chaise for Modern Home Apartment Living Comfort Seekers Minimalists Soft Plush Contemporary Design White</t>
         </is>
       </c>
     </row>
@@ -534,7 +534,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Executive Suite Compact Studio Comfort Seekers Luxury Buyers Adaptable Relaxation Seekers Ultra Soft Plush I...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Turtle Velvet Loveseat Sofa Couch with Chaise for Executive Suite Small Space Comfort Seekers Homeowners Warm Inviting Comfy Premium Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>KEIKI 102" 2Seat Modular Boneless Turtle Velvet Loveseat Sofa Couch with Chaise for Industrial Loft Compact Studio Comfort Seekers Urban Professionals Adaptable Relaxation Seekers Ultra Soft P...</t>
+          <t>KEIKI 102" 2Seat Modular Boneless Sectional Turtle Velvet Loveseat Sofa Couch with Chaise for Urban Loft Bedroom Studio Comfort Seekers Urban Professionals Luxurious Elegant Quality Design Black</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Feminine Retreat Compact Studio Style Conscious Glam Seekers Practical Buyers Luxuriously Soft Designed f...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Feminine Retreat Home Office Style Conscious Glam Seekers Cozy Warm Perfect for Entertaining Refined Design Pink</t>
         </is>
       </c>
     </row>
@@ -654,7 +654,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perf...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Urban Loft Apartment Living Style Conscious Urban Professionals Soft Plush Comfortable Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -695,7 +695,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft L...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch with Chaise Memory Foam for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Premium Design Coffee</t>
         </is>
       </c>
     </row>
@@ -735,7 +735,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Modern Home Compact Studio Style Conscious Homeowners Practical Buyers Luxuriously Soft Great for Intimat...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for City Apartment Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Quality Design Gray</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>KEIKI 54" 2Seat Modular Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Design...</t>
+          <t>KEIKI 54" 2Seat Velvet Loveseat Sofa Couch Rotating Side Table Memory Foam for Cozy Cottage Home Office Style Conscious Traditional Families Cozy Warm Perfect for Refined Design Beige</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Modular Velvet Sofa Couch for Industrial Loft Great Room Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perfect for Bold Sophisticated Relaxation Glam M...</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Urban Loft Apartment Living Style Conscious Urban Professionals Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -853,7 +853,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>KEIKI 172" 6Seat Modular Velvet Sofa Couch for Cozy Cottage Great Room Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Beige</t>
+          <t>KEIKI 172" 6Seat Velvet Sofa Couch for Cozy Cottage Small Space Style Conscious Traditional Families Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige</t>
         </is>
       </c>
     </row>
@@ -892,7 +892,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Modular Velvet Sofa Couch for Industrial Loft Open Concept Living Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Great for Spacious Gathering Area Glam ...</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Urban Loft Bedroom Studio Style Conscious Urban Professionals Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Black</t>
         </is>
       </c>
     </row>
@@ -931,7 +931,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>KEIKI 149" 5Seat Modular Velvet Sofa Couch for Cozy Cottage Open Concept Living Style Conscious Traditional Families Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam Modern...</t>
+          <t>KEIKI 149" 5Seat Velvet Sofa Couch for Cozy Cottage Home Office Style Conscious Traditional Families Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Modular Velvet Loveseat Sofa Couch for Industrial Loft Compact Studio Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Perfect for Bold Sophisticated Relax...</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Urban Loft Apartment Living Style Conscious Urban Professionals Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>KEIKI 63" 2Seat Modular Velvet Loveseat Sofa Couch for Cozy Cottage Compact Studio Style Conscious Traditional Families Practical Buyers Luxuriously Soft Ideal for Luxuriously Soft Lounging Gl...</t>
+          <t>KEIKI 63" 2Seat Velvet Sofa Couch for Cozy Cottage Small Space Style Conscious Traditional Families Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige</t>
         </is>
       </c>
     </row>
@@ -1048,7 +1048,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Modular Velvet Sofa Couch for Cozy Cottage Small Apartment Style Conscious Traditional Families Practical Buyers Luxuriously Soft Great for Functional Relaxation Spot Glam Mode...</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Cozy Cottage Bedroom Studio Style Conscious Traditional Families Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Beige</t>
         </is>
       </c>
     </row>
@@ -1087,7 +1087,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>KEIKI 86" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Practical Buyers Luxuriously Soft Designed for Versatile Layout Glam Modern Black</t>
+          <t>KEIKI 86" 3Seat Velvet Sofa Couch for Urban Loft Home Office Style Conscious Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Black</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Rela...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch with Chaise Memory Foam for City Apartment Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Contemporary Design Gray</t>
         </is>
       </c>
     </row>
@@ -1169,7 +1169,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Ideal for Luxur...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch with Chaise Memory Foam for Urban Loft Small Space Style Conscious Urban Professionals Warm Inviting Comfy Supportive Premium Design Black</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Feminine Retreat Small Apartment Style Conscious Glam Seekers Adaptable Homeowners Luxuriously Soft Great for Functional ...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch with Chaise Memory Foam for Feminine Retreat Bedroom Studio Style Conscious Glam Seekers Luxurious Elegant Sophisticated Quality Design Pink</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch with Chaise Memory Foam for Cozy Cottage Small Apartment Style Conscious Traditional Families Adaptable Homeowners Luxuriously Soft Designed for Flex...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch with Chaise Memory Foam for Cozy Cottage Home Office Style Conscious Traditional Families Cozy Warm Perfect for Refined Design Beige</t>
         </is>
       </c>
     </row>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Industrial Loft Great Room Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Perfect for Bold Sophisticated Relaxation Gl...</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Velvet Sofa Couch for Urban Loft Apartment Living Style Conscious Urban Professionals Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Black</t>
         </is>
       </c>
     </row>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Industrial Loft Open Concept Living Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Velvet Sofa Couch for Urban Loft Small Space Style Conscious Urban Professionals Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Black</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Industrial Loft Family Living Room Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Spac...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Velvet Sofa Couch for Urban Loft Bedroom Studio Style Conscious Urban Professionals Luxurious Elegant Sophisticated Refined Design Stylish Quality Design Black</t>
         </is>
       </c>
     </row>
@@ -1415,7 +1415,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Gla...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Velvet Sofa Couch for Urban Loft Home Office Style Conscious Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Black</t>
         </is>
       </c>
     </row>
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Executive Suite Great Room Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Perfect for Professional Refined Relaxation Glam M...</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Velvet Sofa Couch for Executive Suite Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1497,7 +1497,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Executive Suite Open Concept Living Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam ...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Velvet Sofa Couch for Executive Suite Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1538,7 +1538,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Executive Suite Family Living Room Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Velvet Sofa Couch for Executive Suite Bedroom Studio Style Conscious Homeowners Luxurious Elegant Refined Design Stylish High Quality Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1579,7 +1579,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Executive Suite Small Apartment Style Conscious Luxury Buyers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Velvet Sofa Couch for Executive Suite Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Dark Gray</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Bright Modern Home Great Room Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Perfect for Clean Airy Feel Relaxation Glam Moder...</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Velvet Sofa Couch for Modern Home Apartment Living Style Conscious Minimalists Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design White</t>
         </is>
       </c>
     </row>
@@ -1661,7 +1661,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Bright Modern Home Open Concept Living Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Velvet Sofa Couch for Modern Home Small Space Style Conscious Minimalists Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Bright Modern Home Family Living Room Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Gla...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Velvet Sofa Couch for Modern Home Bedroom Studio Style Conscious Minimalists Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design White</t>
         </is>
       </c>
     </row>
@@ -1743,7 +1743,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Bright Modern Home Small Apartment Style Conscious Minimalists Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mod...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Velvet Sofa Couch for Modern Home Home Office Style Conscious Minimalists Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design White</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>KEIKI 119" 6Seat Modular Velvet Sofa Couch for Modern Home Great Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light Gray</t>
+          <t>KEIKI 119" 6Seat Modular Sectional Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1825,7 +1825,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>KEIKI 119" 5Seat Modular Velvet Sofa Couch for Modern Home Open Concept Living Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern ...</t>
+          <t>KEIKI 119" 5Seat Modular Sectional Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1866,7 +1866,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>KEIKI 119" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
+          <t>KEIKI 119" 4Seat Modular Sectional Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Refined Design Stylish High Quality Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>KEIKI 119" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Ligh...</t>
+          <t>KEIKI 119" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Light Gray</t>
         </is>
       </c>
     </row>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for City Apartment Small Apartment Style Conscious Practical Buyers Adaptable Homeowners Luxuriously Soft Perfect for Balanced Neutral Rel...</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Velvet Sofa Couch with Chaise for City Apartment Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Contemporary Design Grey</t>
         </is>
       </c>
     </row>
@@ -1987,7 +1987,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for City Apartment Compact Studio Style Conscious Practical Buyers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously So...</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Velvet Sofa Couch with Chaise for City Apartment Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Grey</t>
         </is>
       </c>
     </row>
@@ -2027,7 +2027,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot ...</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Velvet Sofa Couch with Chaise for Garden Home Bedroom Studio Style Conscious Nature Lovers Luxurious Elegant Sophisticated Refined Design Quality Design Green</t>
         </is>
       </c>
     </row>
@@ -2067,7 +2067,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configu...</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Velvet Sofa Couch with Chaise for Garden Home Home Office Style Conscious Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Refined Design Green</t>
         </is>
       </c>
     </row>
@@ -2107,7 +2107,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>KEIKI 92" 3Seat Modular Velvet Sofa Couch with Chaise for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam M...</t>
+          <t>KEIKI 92" 3Seat Modular Sectional Velvet Sofa Couch with Chaise for Sunny Apartment Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Contemporary Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>KEIKI 68" 2Seat Modular Velvet Loveseat Sofa Couch with Chaise for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Loungi...</t>
+          <t>KEIKI 68" 2Seat Modular Sectional Velvet Sofa Couch with Chaise for Sunny Apartment Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space ...</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Velvet Sofa Couch with Chaise for City Apartment Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Quality Design Gray</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2227,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuratio...</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Velvet Sofa Couch with Chaise for Garden Home Home Office Style Conscious Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Refined Design Green</t>
         </is>
       </c>
     </row>
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>KEIKI 92" 4Seat Modular Velvet Sofa Couch with Chaise for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Gla...</t>
+          <t>KEIKI 92" 4Seat Modular Sectional Velvet Sofa Couch with Chaise for Sunny Apartment Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Contemporary Design Yellow</t>
         </is>
       </c>
     </row>
@@ -2307,7 +2307,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige White</t>
         </is>
       </c>
     </row>
@@ -2347,7 +2347,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Be...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Beige White</t>
         </is>
       </c>
     </row>
@@ -2387,7 +2387,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Home Home Office Style Conscious Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -2427,7 +2427,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam Mod...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Home Apartment Living Style Conscious Nature Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Green</t>
         </is>
       </c>
     </row>
@@ -2467,7 +2467,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Oasis Family Living Room Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Garden Home Small Space Style Conscious Nature Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Green</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Home Bedroom Studio Style Conscious Nature Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Green</t>
         </is>
       </c>
     </row>
@@ -2547,7 +2547,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern ...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Home Home Office Style Conscious Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design</t>
         </is>
       </c>
     </row>
@@ -2587,7 +2587,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam Modern...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Home Apartment Living Style Conscious Nature Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Green</t>
         </is>
       </c>
     </row>
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern ...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Home Small Space Style Conscious Nature Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Green</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Oasis Small Apartment Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Garden Home Bedroom Studio Style Conscious Nature Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Green</t>
         </is>
       </c>
     </row>
@@ -2707,7 +2707,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam ...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Garden Home Home Office Style Conscious Nature Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Green</t>
         </is>
       </c>
     </row>
@@ -2747,7 +2747,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Perfect for Fresh Natural Relaxation Glam...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Garden Home Apartment Living Style Conscious Nature Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Green</t>
         </is>
       </c>
     </row>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Garden Oasis Compact Studio Style Conscious Plant Parents Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam ...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Garden Home Small Space Style Conscious Nature Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Green</t>
         </is>
       </c>
     </row>
@@ -2827,7 +2827,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Mod...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Blue</t>
         </is>
       </c>
     </row>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Moder...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Home Office Style Conscious Beach Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Family Living Room Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Glam Mo...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Coastal Home Apartment Living Style Conscious Beach Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Blue</t>
         </is>
       </c>
     </row>
@@ -2947,7 +2947,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Blue</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Space Style Conscious Beach Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern ...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Blue</t>
         </is>
       </c>
     </row>
@@ -3027,7 +3027,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Blue</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Home Office Style Conscious Beach Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -3067,7 +3067,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Glam Moder...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Apartment Living Style Conscious Beach Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Blue</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Blue</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Space Style Conscious Beach Lovers Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -3147,7 +3147,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Blue</t>
         </is>
       </c>
     </row>
@@ -3187,7 +3187,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam M...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Coastal Home Home Office Style Conscious Beach Lovers Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Blue</t>
         </is>
       </c>
     </row>
@@ -3227,7 +3227,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Coastal Home Compact Studio Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Perfect for Serene Peaceful Relaxation Gla...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Coastal Home Apartment Living Style Conscious Beach Lovers Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Blue</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3267,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern L...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern L...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -3387,7 +3387,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3427,7 +3427,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Ligh...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -3467,7 +3467,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Lig...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Ligh...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -3547,7 +3547,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Light...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3587,7 +3587,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Intimate Cozy Corner Glam Modern Li...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Light Coffee</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Mode...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Light</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Be...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3747,7 +3747,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern B...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3787,7 +3787,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Modern Home Family Living Room Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Comfortable Gathering Space Glam Modern...</t>
+          <t>KEIKI 137" 4Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Beig...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Beige</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Beige...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3907,7 +3907,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Beig...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium High Quality Premium Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3947,7 +3947,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Bei...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Beige White</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam Modern Beig...</t>
+          <t>KEIKI 107" 3Seat Modular Velvet Sofa Couch for Living Room Home Office Style Conscious Homeowners Cozy Warm Perfect for Entertaining Relaxation Classic Refined High Quality Premium Design Beige</t>
         </is>
       </c>
     </row>
@@ -4027,7 +4027,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>KEIKI 76" 2Seat Modular Velvet Loveseat Sofa Couch for Modern Home Compact Studio Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Moder...</t>
+          <t>KEIKI 76" 2Seat Modular Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Beige White</t>
         </is>
       </c>
     </row>
@@ -4067,7 +4067,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Modern Gray</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for City Apartment Small Space Style Conscious Homeowners Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Gray</t>
         </is>
       </c>
     </row>
@@ -4107,7 +4107,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Coastal Home Small Apartment Style Conscious Beach Lovers Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern ...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Coastal Home Bedroom Studio Style Conscious Beach Lovers Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Blue</t>
         </is>
       </c>
     </row>
@@ -4147,7 +4147,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Industrial Loft Small Apartment Style Conscious Urban Professionals Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Gla...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Urban Loft Home Office Style Conscious Urban Professionals Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Black</t>
         </is>
       </c>
     </row>
@@ -4187,7 +4187,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Perfect for Comfortable Relaxation Glam Modern Dark ...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Apartment Living Style Conscious Homeowners Soft Plush Comfortable Cozy Relaxing Lounge Modern Contemporary Design Dark Green</t>
         </is>
       </c>
     </row>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Feminine Retreat Small Apartment Style Conscious Glam Seekers Adaptable Homeowners Luxuriously Soft Ideal for Luxuriously Soft Lounging Glam Mode...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Feminine Retreat Small Space Style Conscious Glam Seekers Warm Inviting Comfy Supportive Rest Space Elegant Premium Design Pink</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Modern Home Small Apartment Style Conscious Homeowners Adaptable Homeowners Luxuriously Soft Great for Functional Relaxation Spot Glam Modern Coffee</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Living Room Bedroom Studio Style Conscious Homeowners Luxurious Elegant Sophisticated Refined Design Stylish High Quality Design Coffee</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>KEIKI 102" 3Seat Modular Velvet Sofa Couch for Cozy Cottage Small Apartment Style Conscious Traditional Families Adaptable Homeowners Luxuriously Soft Designed for Flexible Configuration Glam ...</t>
+          <t>KEIKI 102" 3Seat Modular Sectional Velvet Sofa Couch for Cozy Cottage Home Office Style Conscious Traditional Families Cozy Warm Perfect for Entertaining Relaxation Classic Refined Design Beige</t>
         </is>
       </c>
     </row>
